--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R559b26ebef914e77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfac38c2dcd4e4855"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfac38c2dcd4e4855"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R26a05948014f4d6c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R26a05948014f4d6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0146f569f24d4a98"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0146f569f24d4a98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0c2c1ecede954500"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0c2c1ecede954500"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra526ac8b463b44b9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra526ac8b463b44b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9c0de89dc01a4e24"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9c0de89dc01a4e24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0382dbfd30a94309"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0382dbfd30a94309"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1b46ce7f9dfb4104"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1b46ce7f9dfb4104"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf1b4c8b17ce44c1f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf1b4c8b17ce44c1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1d081be93d024cc0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1d081be93d024cc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R05810fd7890c4989"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R05810fd7890c4989"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd51c470a51a645f9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd51c470a51a645f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6dbb676639724fbb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/NumberFormats/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6dbb676639724fbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf353512056ac4328"/>
   </x:sheets>
 </x:workbook>
 </file>
